--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-07-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-07-2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDBECE0-5F82-46CE-8CDD-65C23FF2772B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329F502D-500E-46AB-9436-27ED31DC94C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng tính CK" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="82">
   <si>
     <t>STT</t>
   </si>
@@ -265,11 +265,14 @@
 linh kiện dùng cho sủa chữa)</t>
   </si>
   <si>
-    <t>Hết lô</t>
-  </si>
-  <si>
     <t>Tồn lô 2/2026, TG102LE-4G (Aithings giữ 4 thiết bị kiểm tra, Makipos 
 giữ 2 mạch fix lỗi chưa trả) 6 mạch lỗi</t>
+  </si>
+  <si>
+    <t>Hết lô 4</t>
+  </si>
+  <si>
+    <t>Đang xử lý (thực tế nhận 470)</t>
   </si>
 </sst>
 </file>
@@ -280,7 +283,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;[Red]#,##0.0"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,12 +349,6 @@
       <charset val="163"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <i/>
       <sz val="9"/>
       <name val="Times New Roman"/>
@@ -361,12 +358,6 @@
       <i/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -408,12 +399,6 @@
     </font>
     <font>
       <i/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -429,6 +414,12 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -619,16 +610,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -637,70 +625,368 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="14" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="14" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="8"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -709,361 +995,53 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="16" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="16" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1542,339 +1520,339 @@
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" style="6" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" customWidth="1"/>
     <col min="3" max="3" width="24.5703125" customWidth="1"/>
     <col min="4" max="4" width="20.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" style="23" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" style="15" customWidth="1"/>
     <col min="6" max="6" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="90"/>
-      <c r="B1" s="91"/>
-      <c r="C1" s="98" t="s">
+      <c r="A1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="95" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="97"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="103" t="s">
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="105"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="80"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="92" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="94"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="69"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="100" t="str">
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="75" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 31 tháng 07 năm 2026</v>
       </c>
-      <c r="F6" s="100"/>
+      <c r="F6" s="75"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="99" t="s">
+      <c r="A7" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="28"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="28"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="28"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="125" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="80">
+      <c r="A11" s="24">
         <v>1</v>
       </c>
-      <c r="B11" s="80" t="s">
+      <c r="B11" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="80">
+      <c r="C11" s="24">
         <v>330</v>
       </c>
-      <c r="D11" s="81">
+      <c r="D11" s="26">
         <v>8000</v>
       </c>
-      <c r="E11" s="81">
+      <c r="E11" s="26">
         <f>SUM(C11*D11)</f>
         <v>2640000</v>
       </c>
-      <c r="F11" s="80" t="s">
+      <c r="F11" s="24" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="80">
+      <c r="A12" s="24">
         <v>2</v>
       </c>
-      <c r="B12" s="80" t="s">
+      <c r="B12" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="80">
+      <c r="C12" s="24">
         <v>200</v>
       </c>
-      <c r="D12" s="81">
+      <c r="D12" s="26">
         <v>3000</v>
       </c>
-      <c r="E12" s="81">
+      <c r="E12" s="26">
         <f>SUM(C12*D12)</f>
         <v>600000</v>
       </c>
-      <c r="F12" s="80" t="s">
+      <c r="F12" s="24" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="80">
+      <c r="A13" s="24">
         <v>3</v>
       </c>
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="80">
+      <c r="C13" s="24">
         <v>300</v>
       </c>
-      <c r="D13" s="81">
+      <c r="D13" s="26">
         <v>3000</v>
       </c>
-      <c r="E13" s="81">
+      <c r="E13" s="26">
         <f>SUM(C13*D13)</f>
         <v>900000</v>
       </c>
-      <c r="F13" s="80" t="s">
+      <c r="F13" s="24" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="86"/>
-      <c r="C14" s="50">
-        <f>SUM(C13:C13)</f>
-        <v>300</v>
-      </c>
-      <c r="D14" s="51"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="28">
+        <f>SUM(C11:C13)</f>
+        <v>830</v>
+      </c>
+      <c r="D14" s="29"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="87"/>
-      <c r="C15" s="87"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="49">
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="27">
         <f>SUM(E11:E13)</f>
         <v>4140000</v>
       </c>
-      <c r="F15" s="46"/>
+      <c r="F15" s="24"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="28"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="28"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="18"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="88" t="s">
+      <c r="A18" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="88"/>
-      <c r="C18" s="20" t="s">
+      <c r="B18" s="103"/>
+      <c r="C18" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="88" t="s">
+      <c r="D18" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="88"/>
-      <c r="F18" s="9" t="s">
+      <c r="E18" s="103"/>
+      <c r="F18" s="126" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="89" t="s">
+      <c r="A19" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="27" t="s">
+      <c r="B19" s="64"/>
+      <c r="C19" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="89" t="s">
+      <c r="D19" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="89"/>
-      <c r="F19" s="27" t="s">
+      <c r="E19" s="64"/>
+      <c r="F19" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="9"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="126"/>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="9"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="126"/>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="9"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="126"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="126"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="22"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="41"/>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="20" t="s">
+      <c r="B24" s="103"/>
+      <c r="C24" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="88" t="s">
+      <c r="D24" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="88"/>
-      <c r="F24" s="9" t="s">
+      <c r="E24" s="103"/>
+      <c r="F24" s="126" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="8"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="8"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="8"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="11"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="12"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1926,466 +1904,466 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="113"/>
-      <c r="B1" s="114"/>
-      <c r="C1" s="115" t="s">
+      <c r="A1" s="88"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="113"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="124" t="s">
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="126"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="101"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="113"/>
-      <c r="B3" s="114"/>
-      <c r="C3" s="103" t="s">
+      <c r="A3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="105"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="113"/>
-      <c r="B4" s="114"/>
-      <c r="C4" s="92" t="s">
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="94"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="91" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="119"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="94"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="70"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58" t="s">
+      <c r="A6" s="48"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="129" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
     </row>
     <row r="8" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
     </row>
     <row r="9" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
+      <c r="A9" s="130"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="48">
+      <c r="B10" s="96"/>
+      <c r="C10" s="26">
         <f>'Bảng tính CK'!E15</f>
         <v>4140000</v>
       </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="106" t="s">
+      <c r="A11" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="107"/>
-      <c r="C11" s="48">
+      <c r="B11" s="82"/>
+      <c r="C11" s="26">
         <v>3</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="122" t="s">
+      <c r="A12" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="123"/>
-      <c r="C12" s="46">
+      <c r="B12" s="98"/>
+      <c r="C12" s="24">
         <v>0</v>
       </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="111" t="s">
+      <c r="A13" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="112"/>
-      <c r="C13" s="46">
+      <c r="B13" s="87"/>
+      <c r="C13" s="24">
         <f>COUNTIFS(C16:C20, "&gt;=2.5",C16:C20,"&lt;7")</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+    </row>
+    <row r="14" spans="1:8" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+    </row>
+    <row r="15" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-    </row>
-    <row r="14" spans="1:8" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-    </row>
-    <row r="15" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="B15" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="132" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="132" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="132" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="132" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="132" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24">
+        <v>1</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="25">
         <v>0</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="46">
+      <c r="D16" s="57">
         <v>1</v>
       </c>
-      <c r="B16" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="47">
-        <v>0</v>
-      </c>
-      <c r="D16" s="83">
-        <v>1</v>
-      </c>
-      <c r="E16" s="48">
+      <c r="E16" s="26">
         <f>($C$10*D16)/$D$19</f>
         <v>1380000</v>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="26">
         <v>0</v>
       </c>
-      <c r="G16" s="48">
+      <c r="G16" s="26">
         <v>0</v>
       </c>
-      <c r="H16" s="48">
+      <c r="H16" s="26">
         <f>((E16-F16)+($F$21/10))-G16</f>
         <v>1380000</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="46">
+      <c r="A17" s="24">
         <v>2</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="47">
-        <v>0</v>
-      </c>
-      <c r="D17" s="83">
+      <c r="C17" s="25">
+        <v>3</v>
+      </c>
+      <c r="D17" s="57">
         <v>1</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="26">
         <f>($C$10*D17)/$D$19</f>
         <v>1380000</v>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="26">
         <v>0</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="26">
         <v>0</v>
       </c>
-      <c r="H17" s="48">
+      <c r="H17" s="26">
         <f>((E17-F17)+($F$21/10))-G17</f>
         <v>1380000</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="46">
+      <c r="A18" s="24">
         <v>3</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="47">
-        <v>0</v>
-      </c>
-      <c r="D18" s="83">
+      <c r="C18" s="25">
         <v>1</v>
       </c>
-      <c r="E18" s="48">
+      <c r="D18" s="57">
+        <v>1</v>
+      </c>
+      <c r="E18" s="26">
         <f>($C$10*D18)/$D$19</f>
         <v>1380000</v>
       </c>
-      <c r="F18" s="48">
+      <c r="F18" s="26">
         <v>0</v>
       </c>
-      <c r="G18" s="48">
+      <c r="G18" s="26">
         <v>0</v>
       </c>
-      <c r="H18" s="48">
+      <c r="H18" s="26">
         <f>((E18-F18)+($F$21/10))-G18</f>
         <v>1380000</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="84">
+      <c r="B19" s="84"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="58">
         <f>SUM(D16:D18)</f>
         <v>3</v>
       </c>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="54">
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="32">
         <f>IF(OR(C20&gt;=7,C20 =""),0,$C$10/($C$11-$C$12))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="32">
         <f>IF(C20&lt;2.5,0,IF(AND(C20&gt;=2.5,C20&lt;7),(C20-2)*(($C$10/($C$11-$C$12))/7),0))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54">
+      <c r="G20" s="32"/>
+      <c r="H20" s="32">
         <f>IF(AND(C20&lt;=2.5,C20&lt;&gt;""),E20+$F$21/($C$11-$C$13-$C$12),E20-F20)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="74" t="s">
+      <c r="I20" s="50" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="85" t="s">
+      <c r="A21" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="127"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="49">
+      <c r="B21" s="102"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="27">
         <f>SUM(E16:E18)</f>
         <v>4140000</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="27">
         <f>SUM(F16:F20)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="49">
+      <c r="G21" s="27">
         <f>SUM(G16:G18)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="49">
+      <c r="H21" s="27">
         <f>SUM(H16:H18)</f>
         <v>4140000</v>
       </c>
-      <c r="J21" s="5"/>
+      <c r="J21" s="4"/>
     </row>
     <row r="22" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="73" t="s">
+      <c r="A22" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="57"/>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="128" t="s">
+      <c r="A24" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="128"/>
-      <c r="C24" s="128" t="s">
+      <c r="B24" s="103"/>
+      <c r="C24" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="128"/>
-      <c r="E24" s="129" t="s">
+      <c r="D24" s="103"/>
+      <c r="E24" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="129"/>
-      <c r="G24" s="128" t="s">
+      <c r="F24" s="104"/>
+      <c r="G24" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="128"/>
+      <c r="H24" s="103"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="89" t="s">
+      <c r="A25" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="89"/>
-      <c r="C25" s="89" t="s">
+      <c r="B25" s="64"/>
+      <c r="C25" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="89"/>
-      <c r="E25" s="130" t="s">
+      <c r="D25" s="64"/>
+      <c r="E25" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="130"/>
-      <c r="G25" s="89" t="s">
+      <c r="F25" s="105"/>
+      <c r="G25" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="89"/>
+      <c r="H25" s="64"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="56"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="56"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="56"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="63"/>
-      <c r="B29" s="64"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
+      <c r="A29" s="41"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="128" t="s">
+      <c r="A30" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="128"/>
-      <c r="C30" s="128" t="s">
+      <c r="B30" s="103"/>
+      <c r="C30" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="128"/>
-      <c r="E30" s="129" t="s">
+      <c r="D30" s="103"/>
+      <c r="E30" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="129"/>
-      <c r="G30" s="128" t="s">
+      <c r="F30" s="104"/>
+      <c r="G30" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="128"/>
+      <c r="H30" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -2442,566 +2420,568 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="139"/>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="140" t="s">
+      <c r="A1" s="109"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="110" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="146" t="s">
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="116" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="147"/>
+      <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="139"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="146" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="147"/>
+      <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="139"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="145"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="146" t="s">
+      <c r="A3" s="109"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="116" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="147"/>
+      <c r="H3" s="117"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="138" t="str">
+      <c r="A4" s="108" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 31 tháng 07 năm 2026</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="B4" s="108"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="15"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="B5" s="134"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="135"/>
+      <c r="G5" s="135"/>
+      <c r="H5" s="137"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
+      <c r="B6" s="134"/>
+      <c r="C6" s="134"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="134"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="134"/>
+      <c r="H6" s="137"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="134"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="132" t="s">
+      <c r="A8" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="132" t="s">
+      <c r="B8" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="134" t="s">
+      <c r="C8" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="137" t="s">
+      <c r="D8" s="141"/>
+      <c r="E8" s="141"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="143" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="137"/>
-      <c r="I8" s="55"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="33"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="133"/>
-      <c r="B9" s="133"/>
-      <c r="C9" s="37" t="s">
+      <c r="A9" s="144"/>
+      <c r="B9" s="144"/>
+      <c r="C9" s="145" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="145" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="145" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="55"/>
+      <c r="G9" s="143"/>
+      <c r="H9" s="143"/>
+      <c r="I9" s="33"/>
     </row>
     <row r="10" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="79">
+      <c r="A10" s="55">
         <v>1</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="21">
         <v>1000</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="21">
         <v>2</v>
       </c>
-      <c r="E10" s="39">
+      <c r="E10" s="21">
         <v>0</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="21">
         <f>D10-E10</f>
         <v>2</v>
       </c>
-      <c r="G10" s="152" t="s">
+      <c r="G10" s="106" t="s">
         <v>78</v>
       </c>
-      <c r="H10" s="153"/>
-      <c r="I10" s="55"/>
+      <c r="H10" s="107"/>
+      <c r="I10" s="33"/>
     </row>
     <row r="11" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="79">
+      <c r="A11" s="55">
         <v>2</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="21">
         <v>1000</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="21">
         <v>203</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="21">
         <v>191</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="21">
         <f>SUM(D11-E11)</f>
         <v>12</v>
       </c>
-      <c r="G11" s="152" t="s">
-        <v>80</v>
-      </c>
-      <c r="H11" s="153"/>
-      <c r="I11" s="55"/>
+      <c r="G11" s="106" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="107"/>
+      <c r="I11" s="33"/>
     </row>
     <row r="12" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="79">
+      <c r="A12" s="55">
         <v>4</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="21">
         <v>200</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="21">
         <v>200</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="21">
         <v>200</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="21">
         <f>SUM(D12-E12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="152" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="153"/>
-      <c r="I12" s="55"/>
+      <c r="G12" s="106" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="107"/>
+      <c r="I12" s="33"/>
     </row>
     <row r="13" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="79">
+      <c r="A13" s="55">
         <v>5</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="21">
         <v>3000</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="21">
         <v>2800</v>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="21">
         <v>300</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="21">
         <f>SUM(D13-E13)</f>
         <v>2500</v>
       </c>
-      <c r="G13" s="152" t="s">
+      <c r="G13" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="H13" s="153"/>
-      <c r="I13" s="55"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="33"/>
     </row>
     <row r="14" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="79">
+      <c r="A14" s="55">
         <v>6</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="21">
         <v>200</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="21">
         <v>2</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="21">
         <v>0</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="23">
         <f>D14-E14</f>
         <v>2</v>
       </c>
-      <c r="G14" s="131" t="s">
+      <c r="G14" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="131"/>
-      <c r="I14" s="55"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="33"/>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="79">
+      <c r="A15" s="55">
         <v>7</v>
       </c>
-      <c r="B15" s="78" t="s">
+      <c r="B15" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="21">
         <v>200</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="21">
         <v>178</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="21">
         <v>0</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="23">
         <f t="shared" ref="F15" si="0">D15</f>
         <v>178</v>
       </c>
-      <c r="G15" s="131" t="s">
+      <c r="G15" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="131"/>
-      <c r="I15" s="55"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="79">
+      <c r="A16" s="55">
         <v>8</v>
       </c>
-      <c r="B16" s="78" t="s">
+      <c r="B16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="21">
         <v>300</v>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="21">
         <v>52</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="21">
         <v>0</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="23">
         <f>D16-E16</f>
         <v>52</v>
       </c>
-      <c r="G16" s="131" t="s">
+      <c r="G16" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="131"/>
+      <c r="H16" s="122"/>
     </row>
     <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="79">
+      <c r="A17" s="55">
         <v>9</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="39">
+      <c r="C17" s="21">
         <v>200</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="21">
         <v>22</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="21">
         <v>0</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="23">
         <f>D17-E17</f>
         <v>22</v>
       </c>
-      <c r="G17" s="131" t="s">
+      <c r="G17" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="131"/>
+      <c r="H17" s="122"/>
     </row>
     <row r="18" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="79">
+      <c r="A18" s="55">
         <v>10</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="21">
         <v>30</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="21">
         <v>2</v>
       </c>
-      <c r="E18" s="39">
+      <c r="E18" s="21">
         <v>0</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="23">
         <f>D18-E18</f>
         <v>2</v>
       </c>
-      <c r="G18" s="131" t="s">
+      <c r="G18" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="131"/>
+      <c r="H18" s="122"/>
     </row>
     <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="79">
+      <c r="A19" s="55">
         <v>11</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="39">
+      <c r="C19" s="21">
         <v>30</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="21">
         <v>3</v>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="21">
         <v>0</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="23">
         <v>3</v>
       </c>
-      <c r="G19" s="131" t="s">
+      <c r="G19" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="131"/>
+      <c r="H19" s="122"/>
     </row>
     <row r="20" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="79">
+      <c r="A20" s="55">
         <v>12</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39">
+      <c r="C20" s="21"/>
+      <c r="D20" s="21">
+        <v>23</v>
+      </c>
+      <c r="E20" s="21">
         <v>0</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20" s="23">
         <f>SUM(D20-E20)</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="150" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="123" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="151"/>
+      <c r="H20" s="124"/>
     </row>
     <row r="21" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="79">
+      <c r="A21" s="55">
         <v>13</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="39">
+      <c r="C21" s="21">
         <v>500</v>
       </c>
-      <c r="D21" s="39">
-        <v>289</v>
-      </c>
-      <c r="E21" s="39">
+      <c r="D21" s="21">
+        <v>348</v>
+      </c>
+      <c r="E21" s="21">
         <v>208</v>
       </c>
-      <c r="F21" s="41">
+      <c r="F21" s="23">
         <f>SUM(D21-E21)</f>
+        <v>140</v>
+      </c>
+      <c r="G21" s="122" t="s">
         <v>81</v>
       </c>
-      <c r="G21" s="131" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="131"/>
+      <c r="H21" s="122"/>
     </row>
     <row r="22" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="156" t="s">
+      <c r="A22" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="157"/>
-      <c r="C22" s="82">
+      <c r="B22" s="119"/>
+      <c r="C22" s="56">
         <f>SUM(C10:C21)</f>
         <v>6660</v>
       </c>
-      <c r="D22" s="82">
+      <c r="D22" s="56">
         <f>SUM(D10:D21)</f>
-        <v>3753</v>
-      </c>
-      <c r="E22" s="82">
+        <v>3835</v>
+      </c>
+      <c r="E22" s="56">
         <f>SUM(E10:E21)</f>
         <v>899</v>
       </c>
-      <c r="F22" s="82">
+      <c r="F22" s="56">
         <f>SUM(F10:F21)</f>
-        <v>2854</v>
-      </c>
-      <c r="G22" s="148"/>
-      <c r="H22" s="149"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+        <v>2936</v>
+      </c>
+      <c r="G22" s="120"/>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="134"/>
+      <c r="B23" s="134"/>
+      <c r="C23" s="134"/>
+      <c r="D23" s="134"/>
+      <c r="E23" s="134"/>
+      <c r="F23" s="134"/>
+      <c r="G23" s="134"/>
+      <c r="H23" s="134"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="155" t="s">
+      <c r="A24" s="146" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="155"/>
-      <c r="C24" s="155" t="s">
+      <c r="B24" s="146"/>
+      <c r="C24" s="146" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="155"/>
-      <c r="E24" s="155" t="s">
+      <c r="D24" s="146"/>
+      <c r="E24" s="146" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="155"/>
-      <c r="G24" s="88" t="s">
+      <c r="F24" s="146"/>
+      <c r="G24" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="88"/>
+      <c r="H24" s="103"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="89" t="s">
+      <c r="A25" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="89"/>
-      <c r="C25" s="89" t="s">
+      <c r="B25" s="127"/>
+      <c r="C25" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="89"/>
-      <c r="E25" s="89" t="s">
+      <c r="D25" s="127"/>
+      <c r="E25" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="89"/>
-      <c r="G25" s="89" t="s">
+      <c r="F25" s="127"/>
+      <c r="G25" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="89"/>
+      <c r="H25" s="127"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="32"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
+      <c r="A26" s="147"/>
+      <c r="B26" s="147"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="148"/>
+      <c r="G26" s="147"/>
+      <c r="H26" s="147"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="32"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
+      <c r="A27" s="147"/>
+      <c r="B27" s="147"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="147"/>
+      <c r="F27" s="147"/>
+      <c r="G27" s="147"/>
+      <c r="H27" s="147"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="43"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
+      <c r="A28" s="149"/>
+      <c r="B28" s="149"/>
+      <c r="C28" s="149"/>
+      <c r="D28" s="149"/>
+      <c r="E28" s="149"/>
+      <c r="F28" s="150"/>
+      <c r="G28" s="149"/>
+      <c r="H28" s="149"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="43"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
+      <c r="A29" s="149"/>
+      <c r="B29" s="149"/>
+      <c r="C29" s="149"/>
+      <c r="D29" s="149"/>
+      <c r="E29" s="149"/>
+      <c r="F29" s="150"/>
+      <c r="G29" s="149"/>
+      <c r="H29" s="149"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="154" t="s">
+      <c r="A30" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="154"/>
-      <c r="C30" s="154" t="s">
+      <c r="B30" s="151"/>
+      <c r="C30" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="154"/>
-      <c r="E30" s="154" t="s">
+      <c r="D30" s="151"/>
+      <c r="E30" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="154"/>
-      <c r="G30" s="154" t="s">
+      <c r="F30" s="151"/>
+      <c r="G30" s="151" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="154"/>
+      <c r="H30" s="151"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="35"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
+      <c r="A31" s="134"/>
+      <c r="B31" s="134"/>
+      <c r="C31" s="134"/>
+      <c r="D31" s="152"/>
+      <c r="E31" s="134"/>
+      <c r="F31" s="134"/>
+      <c r="G31" s="134"/>
+      <c r="H31" s="134"/>
     </row>
   </sheetData>
   <mergeCells count="36">

--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-07-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-07-2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329F502D-500E-46AB-9436-27ED31DC94C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E961A3-D171-4346-9DA5-7E6537936863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng tính CK" sheetId="1" r:id="rId1"/>
@@ -261,10 +261,6 @@
     <t>Đang xử lý</t>
   </si>
   <si>
-    <t>Tồn lỗi (lỗi PCB bóc 
-linh kiện dùng cho sủa chữa)</t>
-  </si>
-  <si>
     <t>Tồn lô 2/2026, TG102LE-4G (Aithings giữ 4 thiết bị kiểm tra, Makipos 
 giữ 2 mạch fix lỗi chưa trả) 6 mạch lỗi</t>
   </si>
@@ -273,6 +269,10 @@
   </si>
   <si>
     <t>Đang xử lý (thực tế nhận 470)</t>
+  </si>
+  <si>
+    <t>Tồn lỗi (lỗi PCB bóc 
+linh kiện dùng cho sửa chữa)</t>
   </si>
 </sst>
 </file>
@@ -776,201 +776,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1002,9 +811,227 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="8"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1016,33 +1043,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1529,74 +1529,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="65"/>
-      <c r="B1" s="66"/>
-      <c r="C1" s="73" t="s">
+      <c r="A1" s="80"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="70" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="72"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="87"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="78" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="80"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="95"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="67" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="69"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="84"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="43"/>
       <c r="C6" s="43"/>
       <c r="D6" s="44"/>
-      <c r="E6" s="75" t="str">
+      <c r="E6" s="90" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 31 tháng 07 năm 2026</v>
       </c>
-      <c r="F6" s="75"/>
+      <c r="F6" s="90"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89"/>
       <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1627,7 +1627,7 @@
       <c r="C10" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="125" t="s">
+      <c r="D10" s="61" t="s">
         <v>45</v>
       </c>
       <c r="E10" s="28" t="s">
@@ -1701,10 +1701,10 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="62"/>
+      <c r="B14" s="97"/>
       <c r="C14" s="28">
         <f>SUM(C11:C13)</f>
         <v>830</v>
@@ -1714,12 +1714,12 @@
       <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
       <c r="E15" s="27">
         <f>SUM(E11:E13)</f>
         <v>4140000</v>
@@ -1743,33 +1743,33 @@
       <c r="F17" s="18"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="103" t="s">
+      <c r="A18" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="103"/>
+      <c r="B18" s="99"/>
       <c r="C18" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="103" t="s">
+      <c r="D18" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="103"/>
-      <c r="F18" s="126" t="s">
+      <c r="E18" s="99"/>
+      <c r="F18" s="62" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="64"/>
+      <c r="B19" s="100"/>
       <c r="C19" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="64" t="s">
+      <c r="D19" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="64"/>
+      <c r="E19" s="100"/>
       <c r="F19" s="17" t="s">
         <v>7</v>
       </c>
@@ -1778,47 +1778,47 @@
       <c r="A20" s="34"/>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
-      <c r="D20" s="126"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="60"/>
-      <c r="F20" s="126"/>
+      <c r="F20" s="62"/>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34"/>
       <c r="B21" s="34"/>
       <c r="C21" s="34"/>
-      <c r="D21" s="126"/>
+      <c r="D21" s="62"/>
       <c r="E21" s="60"/>
-      <c r="F21" s="126"/>
+      <c r="F21" s="62"/>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="34"/>
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
-      <c r="D22" s="126"/>
+      <c r="D22" s="62"/>
       <c r="E22" s="60"/>
-      <c r="F22" s="126"/>
+      <c r="F22" s="62"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41"/>
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
-      <c r="D23" s="128"/>
+      <c r="D23" s="63"/>
       <c r="E23" s="60"/>
       <c r="F23" s="41"/>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="103" t="s">
+      <c r="A24" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="103"/>
+      <c r="B24" s="99"/>
       <c r="C24" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="103" t="s">
+      <c r="D24" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="103"/>
-      <c r="F24" s="126" t="s">
+      <c r="E24" s="99"/>
+      <c r="F24" s="62" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1856,6 +1856,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D24:E24"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C2:F2"/>
@@ -1864,14 +1872,6 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="C3:F3"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D24:E24"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1904,64 +1904,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="88"/>
-      <c r="B1" s="89"/>
-      <c r="C1" s="90" t="s">
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="88"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="99" t="s">
+      <c r="A2" s="111"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="101"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="124"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="88"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="78" t="s">
+      <c r="A3" s="111"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="80"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="95"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="67" t="s">
+      <c r="A4" s="111"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="69"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="84"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="114" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="94"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="117"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="48"/>
@@ -1976,7 +1976,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="129" t="s">
+      <c r="A7" s="64" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="35"/>
@@ -2000,7 +2000,7 @@
       <c r="H8" s="35"/>
     </row>
     <row r="9" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="130"/>
+      <c r="A9" s="65"/>
       <c r="B9" s="40"/>
       <c r="C9" s="35"/>
       <c r="D9" s="35"/>
@@ -2010,39 +2010,39 @@
       <c r="H9" s="35"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="95" t="s">
+      <c r="A10" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="96"/>
+      <c r="B10" s="119"/>
       <c r="C10" s="26">
         <f>'Bảng tính CK'!E15</f>
         <v>4140000</v>
       </c>
-      <c r="D10" s="131"/>
+      <c r="D10" s="66"/>
       <c r="E10" s="35"/>
       <c r="F10" s="35"/>
       <c r="G10" s="35"/>
       <c r="H10" s="35"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="81" t="s">
+      <c r="A11" s="104" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="82"/>
+      <c r="B11" s="105"/>
       <c r="C11" s="26">
         <v>3</v>
       </c>
-      <c r="D11" s="131"/>
+      <c r="D11" s="66"/>
       <c r="E11" s="35"/>
       <c r="F11" s="35"/>
       <c r="G11" s="35"/>
       <c r="H11" s="35"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="98"/>
+      <c r="B12" s="121"/>
       <c r="C12" s="24">
         <v>0</v>
       </c>
@@ -2053,10 +2053,10 @@
       <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="87"/>
+      <c r="B13" s="110"/>
       <c r="C13" s="24">
         <f>COUNTIFS(C16:C20, "&gt;=2.5",C16:C20,"&lt;7")</f>
         <v>1</v>
@@ -2087,19 +2087,19 @@
       <c r="C15" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="132" t="s">
+      <c r="D15" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="132" t="s">
+      <c r="E15" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="132" t="s">
+      <c r="F15" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="132" t="s">
+      <c r="G15" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="H15" s="132" t="s">
+      <c r="H15" s="67" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2188,11 +2188,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="83" t="s">
+      <c r="A19" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="84"/>
-      <c r="C19" s="85"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="108"/>
       <c r="D19" s="58">
         <f>SUM(D16:D18)</f>
         <v>3</v>
@@ -2225,11 +2225,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="61" t="s">
+      <c r="A21" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="102"/>
-      <c r="C21" s="62"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="97"/>
       <c r="D21" s="19"/>
       <c r="E21" s="27">
         <f>SUM(E16:E18)</f>
@@ -2272,40 +2272,40 @@
       <c r="H23" s="35"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="103" t="s">
+      <c r="A24" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="103"/>
-      <c r="C24" s="103" t="s">
+      <c r="B24" s="99"/>
+      <c r="C24" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="103"/>
-      <c r="E24" s="104" t="s">
+      <c r="D24" s="99"/>
+      <c r="E24" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="104"/>
-      <c r="G24" s="103" t="s">
+      <c r="F24" s="102"/>
+      <c r="G24" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="103"/>
+      <c r="H24" s="99"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="64" t="s">
+      <c r="A25" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="64"/>
-      <c r="C25" s="64" t="s">
+      <c r="B25" s="100"/>
+      <c r="C25" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="64"/>
-      <c r="E25" s="105" t="s">
+      <c r="D25" s="100"/>
+      <c r="E25" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="105"/>
-      <c r="G25" s="64" t="s">
+      <c r="F25" s="103"/>
+      <c r="G25" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="64"/>
+      <c r="H25" s="100"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="34"/>
@@ -2348,25 +2348,36 @@
       <c r="H29" s="35"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="103" t="s">
+      <c r="A30" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="103"/>
-      <c r="C30" s="103" t="s">
+      <c r="B30" s="99"/>
+      <c r="C30" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="103"/>
-      <c r="E30" s="104" t="s">
+      <c r="D30" s="99"/>
+      <c r="E30" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="104"/>
-      <c r="G30" s="103" t="s">
+      <c r="F30" s="102"/>
+      <c r="G30" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="103"/>
+      <c r="H30" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A30:B30"/>
@@ -2380,17 +2391,6 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
@@ -2420,126 +2420,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="109"/>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="110" t="s">
+      <c r="A1" s="138"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="139" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="116" t="s">
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="117"/>
+      <c r="H1" s="146"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="109"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="116" t="s">
+      <c r="A2" s="138"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="117"/>
+      <c r="H2" s="146"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="109"/>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="116" t="s">
+      <c r="A3" s="138"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="117"/>
+      <c r="H3" s="146"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="108" t="str">
+      <c r="A4" s="137" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 31 tháng 07 năm 2026</v>
       </c>
-      <c r="B4" s="108"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="133" t="s">
+      <c r="A5" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="135"/>
-      <c r="G5" s="135"/>
-      <c r="H5" s="137"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="72"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="133" t="s">
+      <c r="A6" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="134"/>
-      <c r="C6" s="134"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="134"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="137"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="72"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="134"/>
-      <c r="B7" s="134"/>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134"/>
-      <c r="E7" s="134"/>
-      <c r="F7" s="134"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="134"/>
+      <c r="A7" s="69"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="139" t="s">
+      <c r="A8" s="147" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="139" t="s">
+      <c r="B8" s="147" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="140" t="s">
+      <c r="C8" s="149" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="141"/>
-      <c r="E8" s="141"/>
-      <c r="F8" s="142"/>
-      <c r="G8" s="143" t="s">
+      <c r="D8" s="150"/>
+      <c r="E8" s="150"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="152" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="143"/>
+      <c r="H8" s="152"/>
       <c r="I8" s="33"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
-      <c r="B9" s="144"/>
-      <c r="C9" s="145" t="s">
+      <c r="A9" s="148"/>
+      <c r="B9" s="148"/>
+      <c r="C9" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="145" t="s">
+      <c r="D9" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="145" t="s">
+      <c r="E9" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="145" t="s">
+      <c r="F9" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="143"/>
-      <c r="H9" s="143"/>
+      <c r="G9" s="152"/>
+      <c r="H9" s="152"/>
       <c r="I9" s="33"/>
     </row>
     <row r="10" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2562,10 +2562,10 @@
         <f>D10-E10</f>
         <v>2</v>
       </c>
-      <c r="G10" s="106" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="107"/>
+      <c r="G10" s="125" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="126"/>
       <c r="I10" s="33"/>
     </row>
     <row r="11" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2588,10 +2588,10 @@
         <f>SUM(D11-E11)</f>
         <v>12</v>
       </c>
-      <c r="G11" s="106" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" s="107"/>
+      <c r="G11" s="125" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="126"/>
       <c r="I11" s="33"/>
     </row>
     <row r="12" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2614,10 +2614,10 @@
         <f>SUM(D12-E12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="106" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="107"/>
+      <c r="G12" s="125" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="126"/>
       <c r="I12" s="33"/>
     </row>
     <row r="13" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2640,10 +2640,10 @@
         <f>SUM(D13-E13)</f>
         <v>2500</v>
       </c>
-      <c r="G13" s="106" t="s">
+      <c r="G13" s="125" t="s">
         <v>64</v>
       </c>
-      <c r="H13" s="107"/>
+      <c r="H13" s="126"/>
       <c r="I13" s="33"/>
     </row>
     <row r="14" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2666,10 +2666,10 @@
         <f>D14-E14</f>
         <v>2</v>
       </c>
-      <c r="G14" s="122" t="s">
+      <c r="G14" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="122"/>
+      <c r="H14" s="130"/>
       <c r="I14" s="33"/>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2692,10 +2692,10 @@
         <f t="shared" ref="F15" si="0">D15</f>
         <v>178</v>
       </c>
-      <c r="G15" s="122" t="s">
+      <c r="G15" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="122"/>
+      <c r="H15" s="130"/>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2718,10 +2718,10 @@
         <f>D16-E16</f>
         <v>52</v>
       </c>
-      <c r="G16" s="122" t="s">
+      <c r="G16" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="122"/>
+      <c r="H16" s="130"/>
     </row>
     <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55">
@@ -2743,10 +2743,10 @@
         <f>D17-E17</f>
         <v>22</v>
       </c>
-      <c r="G17" s="122" t="s">
+      <c r="G17" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="122"/>
+      <c r="H17" s="130"/>
     </row>
     <row r="18" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="55">
@@ -2768,10 +2768,10 @@
         <f>D18-E18</f>
         <v>2</v>
       </c>
-      <c r="G18" s="122" t="s">
+      <c r="G18" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="122"/>
+      <c r="H18" s="130"/>
     </row>
     <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="55">
@@ -2792,10 +2792,10 @@
       <c r="F19" s="23">
         <v>3</v>
       </c>
-      <c r="G19" s="122" t="s">
+      <c r="G19" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="122"/>
+      <c r="H19" s="130"/>
     </row>
     <row r="20" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="55">
@@ -2815,10 +2815,10 @@
         <f>SUM(D20-E20)</f>
         <v>23</v>
       </c>
-      <c r="G20" s="123" t="s">
+      <c r="G20" s="135" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="124"/>
+      <c r="H20" s="136"/>
     </row>
     <row r="21" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="55">
@@ -2840,16 +2840,16 @@
         <f>SUM(D21-E21)</f>
         <v>140</v>
       </c>
-      <c r="G21" s="122" t="s">
-        <v>81</v>
-      </c>
-      <c r="H21" s="122"/>
+      <c r="G21" s="130" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="130"/>
     </row>
     <row r="22" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="118" t="s">
+      <c r="A22" s="131" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="119"/>
+      <c r="B22" s="132"/>
       <c r="C22" s="56">
         <f>SUM(C10:C21)</f>
         <v>6660</v>
@@ -2866,125 +2866,145 @@
         <f>SUM(F10:F21)</f>
         <v>2936</v>
       </c>
-      <c r="G22" s="120"/>
-      <c r="H22" s="121"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="134"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="134"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="134"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="134"/>
-      <c r="F23" s="134"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="134"/>
+      <c r="A23" s="69"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="146" t="s">
+      <c r="A24" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="146"/>
-      <c r="C24" s="146" t="s">
+      <c r="B24" s="129"/>
+      <c r="C24" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="146"/>
-      <c r="E24" s="146" t="s">
+      <c r="D24" s="129"/>
+      <c r="E24" s="129" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="146"/>
-      <c r="G24" s="103" t="s">
+      <c r="F24" s="129"/>
+      <c r="G24" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="103"/>
+      <c r="H24" s="99"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="127" t="s">
+      <c r="A25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="127"/>
-      <c r="C25" s="127" t="s">
+      <c r="B25" s="128"/>
+      <c r="C25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="127"/>
-      <c r="E25" s="127" t="s">
+      <c r="D25" s="128"/>
+      <c r="E25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127" t="s">
+      <c r="F25" s="128"/>
+      <c r="G25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="127"/>
+      <c r="H25" s="128"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="147"/>
-      <c r="B26" s="147"/>
-      <c r="C26" s="147"/>
-      <c r="D26" s="147"/>
-      <c r="E26" s="147"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="147"/>
-      <c r="H26" s="147"/>
+      <c r="A26" s="75"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="147"/>
-      <c r="B27" s="147"/>
-      <c r="C27" s="147"/>
+      <c r="A27" s="75"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="75"/>
       <c r="D27" s="59"/>
-      <c r="E27" s="147"/>
-      <c r="F27" s="147"/>
-      <c r="G27" s="147"/>
-      <c r="H27" s="147"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="149"/>
-      <c r="B28" s="149"/>
-      <c r="C28" s="149"/>
-      <c r="D28" s="149"/>
-      <c r="E28" s="149"/>
-      <c r="F28" s="150"/>
-      <c r="G28" s="149"/>
-      <c r="H28" s="149"/>
+      <c r="A28" s="77"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="78"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="149"/>
-      <c r="B29" s="149"/>
-      <c r="C29" s="149"/>
-      <c r="D29" s="149"/>
-      <c r="E29" s="149"/>
-      <c r="F29" s="150"/>
-      <c r="G29" s="149"/>
-      <c r="H29" s="149"/>
+      <c r="A29" s="77"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="77"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="151" t="s">
+      <c r="A30" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="151"/>
-      <c r="C30" s="151" t="s">
+      <c r="B30" s="127"/>
+      <c r="C30" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="151"/>
-      <c r="E30" s="151" t="s">
+      <c r="D30" s="127"/>
+      <c r="E30" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="151"/>
-      <c r="G30" s="151" t="s">
+      <c r="F30" s="127"/>
+      <c r="G30" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="151"/>
+      <c r="H30" s="127"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="134"/>
-      <c r="B31" s="134"/>
-      <c r="C31" s="134"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="134"/>
-      <c r="F31" s="134"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="134"/>
+      <c r="A31" s="69"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H9"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G13:H13"/>
@@ -3001,26 +3021,6 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-07-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-07-2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E961A3-D171-4346-9DA5-7E6537936863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8E98A3-61F7-4BC8-BE98-B9E6EF7BEAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng tính CK" sheetId="1" r:id="rId1"/>
@@ -829,6 +829,21 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -877,19 +892,67 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -901,75 +964,77 @@
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="7"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -978,71 +1043,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1529,74 +1529,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="80"/>
-      <c r="B1" s="81"/>
-      <c r="C1" s="88" t="s">
+      <c r="A1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="85" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="87"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="93" t="s">
+      <c r="A3" s="85"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="95"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="100"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="82" t="s">
+      <c r="A4" s="85"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="84"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="89"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="96" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="92"/>
-      <c r="D5" s="92"/>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="43"/>
       <c r="C6" s="43"/>
       <c r="D6" s="44"/>
-      <c r="E6" s="90" t="str">
+      <c r="E6" s="95" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 31 tháng 07 năm 2026</v>
       </c>
-      <c r="F6" s="90"/>
+      <c r="F6" s="95"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="89"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
       <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1701,10 +1701,10 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="96" t="s">
+      <c r="A14" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="97"/>
+      <c r="B14" s="81"/>
       <c r="C14" s="28">
         <f>SUM(C11:C13)</f>
         <v>830</v>
@@ -1714,12 +1714,12 @@
       <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="98"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
       <c r="E15" s="27">
         <f>SUM(E11:E13)</f>
         <v>4140000</v>
@@ -1743,33 +1743,33 @@
       <c r="F17" s="18"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="99"/>
+      <c r="B18" s="83"/>
       <c r="C18" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="99" t="s">
+      <c r="D18" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="99"/>
+      <c r="E18" s="83"/>
       <c r="F18" s="62" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="100" t="s">
+      <c r="A19" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="100"/>
+      <c r="B19" s="84"/>
       <c r="C19" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="100" t="s">
+      <c r="D19" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="100"/>
+      <c r="E19" s="84"/>
       <c r="F19" s="17" t="s">
         <v>7</v>
       </c>
@@ -1807,17 +1807,17 @@
       <c r="F23" s="41"/>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="99" t="s">
+      <c r="A24" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="99"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="99" t="s">
+      <c r="D24" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="99"/>
+      <c r="E24" s="83"/>
       <c r="F24" s="62" t="s">
         <v>9</v>
       </c>
@@ -1856,6 +1856,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A18:B18"/>
@@ -1864,14 +1872,6 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="C3:F3"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1904,64 +1904,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="111"/>
-      <c r="B1" s="112"/>
-      <c r="C1" s="113" t="s">
+      <c r="A1" s="108"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="110" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="111"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="122" t="s">
+      <c r="A2" s="108"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="119" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="124"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="121"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="111"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="93" t="s">
+      <c r="A3" s="108"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="95"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="100"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="111"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="82" t="s">
+      <c r="A4" s="108"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="84"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="89"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="111" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="115"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="117"/>
+      <c r="B5" s="112"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="114"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="48"/>
@@ -2010,10 +2010,10 @@
       <c r="H9" s="35"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="118" t="s">
+      <c r="A10" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="119"/>
+      <c r="B10" s="116"/>
       <c r="C10" s="26">
         <f>'Bảng tính CK'!E15</f>
         <v>4140000</v>
@@ -2025,10 +2025,10 @@
       <c r="H10" s="35"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="104" t="s">
+      <c r="A11" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="105"/>
+      <c r="B11" s="102"/>
       <c r="C11" s="26">
         <v>3</v>
       </c>
@@ -2039,10 +2039,10 @@
       <c r="H11" s="35"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="120" t="s">
+      <c r="A12" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="121"/>
+      <c r="B12" s="118"/>
       <c r="C12" s="24">
         <v>0</v>
       </c>
@@ -2053,10 +2053,10 @@
       <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="109" t="s">
+      <c r="A13" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="110"/>
+      <c r="B13" s="107"/>
       <c r="C13" s="24">
         <f>COUNTIFS(C16:C20, "&gt;=2.5",C16:C20,"&lt;7")</f>
         <v>1</v>
@@ -2188,11 +2188,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="106" t="s">
+      <c r="A19" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="107"/>
-      <c r="C19" s="108"/>
+      <c r="B19" s="104"/>
+      <c r="C19" s="105"/>
       <c r="D19" s="58">
         <f>SUM(D16:D18)</f>
         <v>3</v>
@@ -2225,11 +2225,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="96" t="s">
+      <c r="A21" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="101"/>
-      <c r="C21" s="97"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="81"/>
       <c r="D21" s="19"/>
       <c r="E21" s="27">
         <f>SUM(E16:E18)</f>
@@ -2272,40 +2272,40 @@
       <c r="H23" s="35"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="99" t="s">
+      <c r="A24" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="99"/>
-      <c r="C24" s="99" t="s">
+      <c r="B24" s="83"/>
+      <c r="C24" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="99"/>
-      <c r="E24" s="102" t="s">
+      <c r="D24" s="83"/>
+      <c r="E24" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="102"/>
-      <c r="G24" s="99" t="s">
+      <c r="F24" s="123"/>
+      <c r="G24" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="99"/>
+      <c r="H24" s="83"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="100" t="s">
+      <c r="A25" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="100"/>
-      <c r="C25" s="100" t="s">
+      <c r="B25" s="84"/>
+      <c r="C25" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="100"/>
-      <c r="E25" s="103" t="s">
+      <c r="D25" s="84"/>
+      <c r="E25" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="103"/>
-      <c r="G25" s="100" t="s">
+      <c r="F25" s="124"/>
+      <c r="G25" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="100"/>
+      <c r="H25" s="84"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="34"/>
@@ -2348,36 +2348,25 @@
       <c r="H29" s="35"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="99" t="s">
+      <c r="A30" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="99"/>
-      <c r="C30" s="99" t="s">
+      <c r="B30" s="83"/>
+      <c r="C30" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="99"/>
-      <c r="E30" s="102" t="s">
+      <c r="D30" s="83"/>
+      <c r="E30" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="102"/>
-      <c r="G30" s="99" t="s">
+      <c r="F30" s="123"/>
+      <c r="G30" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="99"/>
+      <c r="H30" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A30:B30"/>
@@ -2391,6 +2380,17 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
@@ -2420,55 +2420,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="138"/>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="139" t="s">
+      <c r="A1" s="134"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="135" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="145" t="s">
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="146"/>
+      <c r="H1" s="142"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138"/>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="145" t="s">
+      <c r="A2" s="134"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="141" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="146"/>
+      <c r="H2" s="142"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="138"/>
-      <c r="B3" s="138"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="145" t="s">
+      <c r="A3" s="134"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="146"/>
+      <c r="H3" s="142"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="137" t="str">
+      <c r="A4" s="133" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 31 tháng 07 năm 2026</v>
       </c>
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
+      <c r="B4" s="133"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="133"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
@@ -2505,27 +2505,27 @@
       <c r="H7" s="69"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="147" t="s">
+      <c r="A8" s="127" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="147" t="s">
+      <c r="B8" s="127" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="149" t="s">
+      <c r="C8" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="150"/>
-      <c r="E8" s="150"/>
-      <c r="F8" s="151"/>
-      <c r="G8" s="152" t="s">
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="152"/>
+      <c r="H8" s="132"/>
       <c r="I8" s="33"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="148"/>
-      <c r="B9" s="148"/>
+      <c r="A9" s="128"/>
+      <c r="B9" s="128"/>
       <c r="C9" s="74" t="s">
         <v>60</v>
       </c>
@@ -2538,8 +2538,8 @@
       <c r="F9" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="152"/>
-      <c r="H9" s="152"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
       <c r="I9" s="33"/>
     </row>
     <row r="10" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2579,10 +2579,10 @@
         <v>1000</v>
       </c>
       <c r="D11" s="21">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="E11" s="21">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="F11" s="21">
         <f>SUM(D11-E11)</f>
@@ -2666,10 +2666,10 @@
         <f>D14-E14</f>
         <v>2</v>
       </c>
-      <c r="G14" s="130" t="s">
+      <c r="G14" s="147" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="130"/>
+      <c r="H14" s="147"/>
       <c r="I14" s="33"/>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2692,10 +2692,10 @@
         <f t="shared" ref="F15" si="0">D15</f>
         <v>178</v>
       </c>
-      <c r="G15" s="130" t="s">
+      <c r="G15" s="147" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="130"/>
+      <c r="H15" s="147"/>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2718,10 +2718,10 @@
         <f>D16-E16</f>
         <v>52</v>
       </c>
-      <c r="G16" s="130" t="s">
+      <c r="G16" s="147" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="130"/>
+      <c r="H16" s="147"/>
     </row>
     <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55">
@@ -2743,10 +2743,10 @@
         <f>D17-E17</f>
         <v>22</v>
       </c>
-      <c r="G17" s="130" t="s">
+      <c r="G17" s="147" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="130"/>
+      <c r="H17" s="147"/>
     </row>
     <row r="18" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="55">
@@ -2768,10 +2768,10 @@
         <f>D18-E18</f>
         <v>2</v>
       </c>
-      <c r="G18" s="130" t="s">
+      <c r="G18" s="147" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="130"/>
+      <c r="H18" s="147"/>
     </row>
     <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="55">
@@ -2792,10 +2792,10 @@
       <c r="F19" s="23">
         <v>3</v>
       </c>
-      <c r="G19" s="130" t="s">
+      <c r="G19" s="147" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="130"/>
+      <c r="H19" s="147"/>
     </row>
     <row r="20" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="55">
@@ -2815,10 +2815,10 @@
         <f>SUM(D20-E20)</f>
         <v>23</v>
       </c>
-      <c r="G20" s="135" t="s">
+      <c r="G20" s="148" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="136"/>
+      <c r="H20" s="149"/>
     </row>
     <row r="21" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="55">
@@ -2840,34 +2840,34 @@
         <f>SUM(D21-E21)</f>
         <v>140</v>
       </c>
-      <c r="G21" s="130" t="s">
+      <c r="G21" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="H21" s="130"/>
+      <c r="H21" s="147"/>
     </row>
     <row r="22" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="131" t="s">
+      <c r="A22" s="143" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="132"/>
+      <c r="B22" s="144"/>
       <c r="C22" s="56">
         <f>SUM(C10:C21)</f>
         <v>6660</v>
       </c>
       <c r="D22" s="56">
         <f>SUM(D10:D21)</f>
-        <v>3835</v>
+        <v>3644</v>
       </c>
       <c r="E22" s="56">
         <f>SUM(E10:E21)</f>
-        <v>899</v>
+        <v>708</v>
       </c>
       <c r="F22" s="56">
         <f>SUM(F10:F21)</f>
         <v>2936</v>
       </c>
-      <c r="G22" s="133"/>
-      <c r="H22" s="134"/>
+      <c r="G22" s="145"/>
+      <c r="H22" s="146"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="69"/>
@@ -2880,40 +2880,40 @@
       <c r="H23" s="69"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="129" t="s">
+      <c r="A24" s="152" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="129"/>
-      <c r="C24" s="129" t="s">
+      <c r="B24" s="152"/>
+      <c r="C24" s="152" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="129"/>
-      <c r="E24" s="129" t="s">
+      <c r="D24" s="152"/>
+      <c r="E24" s="152" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="129"/>
-      <c r="G24" s="99" t="s">
+      <c r="F24" s="152"/>
+      <c r="G24" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="99"/>
+      <c r="H24" s="83"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="128" t="s">
+      <c r="A25" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="128"/>
-      <c r="C25" s="128" t="s">
+      <c r="B25" s="151"/>
+      <c r="C25" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="128"/>
-      <c r="E25" s="128" t="s">
+      <c r="D25" s="151"/>
+      <c r="E25" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="128"/>
-      <c r="G25" s="128" t="s">
+      <c r="F25" s="151"/>
+      <c r="G25" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="128"/>
+      <c r="H25" s="151"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="75"/>
@@ -2956,22 +2956,22 @@
       <c r="H29" s="77"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="127" t="s">
+      <c r="A30" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="127"/>
-      <c r="C30" s="127" t="s">
+      <c r="B30" s="150"/>
+      <c r="C30" s="150" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="127" t="s">
+      <c r="D30" s="150"/>
+      <c r="E30" s="150" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="127"/>
-      <c r="G30" s="127" t="s">
+      <c r="F30" s="150"/>
+      <c r="G30" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="127"/>
+      <c r="H30" s="150"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="69"/>
@@ -2985,26 +2985,6 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H9"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G13:H13"/>
@@ -3021,6 +3001,26 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-07-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-07-2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8E98A3-61F7-4BC8-BE98-B9E6EF7BEAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C842F3AA-12BB-4C3A-813B-D108DF0D3F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng tính CK" sheetId="1" r:id="rId1"/>
@@ -829,21 +829,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -892,6 +877,30 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="8"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="7"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -955,21 +964,68 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -987,62 +1043,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1529,74 +1529,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="85"/>
-      <c r="B1" s="86"/>
-      <c r="C1" s="93" t="s">
+      <c r="A1" s="80"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="85"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="90" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="87"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="85"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="98" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="100"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="95"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="85"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="87" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="89"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="84"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="43"/>
       <c r="C6" s="43"/>
       <c r="D6" s="44"/>
-      <c r="E6" s="95" t="str">
+      <c r="E6" s="90" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 31 tháng 07 năm 2026</v>
       </c>
-      <c r="F6" s="95"/>
+      <c r="F6" s="90"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89"/>
       <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1701,10 +1701,10 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="81"/>
+      <c r="B14" s="97"/>
       <c r="C14" s="28">
         <f>SUM(C11:C13)</f>
         <v>830</v>
@@ -1714,12 +1714,12 @@
       <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="82" t="s">
+      <c r="A15" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
       <c r="E15" s="27">
         <f>SUM(E11:E13)</f>
         <v>4140000</v>
@@ -1743,33 +1743,33 @@
       <c r="F17" s="18"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83" t="s">
+      <c r="A18" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="83"/>
+      <c r="B18" s="99"/>
       <c r="C18" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="83" t="s">
+      <c r="D18" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="83"/>
+      <c r="E18" s="99"/>
       <c r="F18" s="62" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="84" t="s">
+      <c r="A19" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="84"/>
+      <c r="B19" s="100"/>
       <c r="C19" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="84" t="s">
+      <c r="D19" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="84"/>
+      <c r="E19" s="100"/>
       <c r="F19" s="17" t="s">
         <v>7</v>
       </c>
@@ -1807,17 +1807,17 @@
       <c r="F23" s="41"/>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="83" t="s">
+      <c r="A24" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="83"/>
+      <c r="B24" s="99"/>
       <c r="C24" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="83" t="s">
+      <c r="D24" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="83"/>
+      <c r="E24" s="99"/>
       <c r="F24" s="62" t="s">
         <v>9</v>
       </c>
@@ -1856,6 +1856,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D24:E24"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C2:F2"/>
@@ -1864,14 +1872,6 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="C3:F3"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D24:E24"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1904,64 +1904,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="108"/>
-      <c r="B1" s="109"/>
-      <c r="C1" s="110" t="s">
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="108"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="119" t="s">
+      <c r="A2" s="111"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="121"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="124"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="108"/>
-      <c r="B3" s="109"/>
-      <c r="C3" s="98" t="s">
+      <c r="A3" s="111"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="100"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="95"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="108"/>
-      <c r="B4" s="109"/>
-      <c r="C4" s="87" t="s">
+      <c r="A4" s="111"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="89"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="84"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="114" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="112"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="114"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="117"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="48"/>
@@ -2010,10 +2010,10 @@
       <c r="H9" s="35"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="116"/>
+      <c r="B10" s="119"/>
       <c r="C10" s="26">
         <f>'Bảng tính CK'!E15</f>
         <v>4140000</v>
@@ -2025,10 +2025,10 @@
       <c r="H10" s="35"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="101" t="s">
+      <c r="A11" s="104" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="102"/>
+      <c r="B11" s="105"/>
       <c r="C11" s="26">
         <v>3</v>
       </c>
@@ -2039,10 +2039,10 @@
       <c r="H11" s="35"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="117" t="s">
+      <c r="A12" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="118"/>
+      <c r="B12" s="121"/>
       <c r="C12" s="24">
         <v>0</v>
       </c>
@@ -2053,10 +2053,10 @@
       <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="107"/>
+      <c r="B13" s="110"/>
       <c r="C13" s="24">
         <f>COUNTIFS(C16:C20, "&gt;=2.5",C16:C20,"&lt;7")</f>
         <v>1</v>
@@ -2188,11 +2188,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="103" t="s">
+      <c r="A19" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="104"/>
-      <c r="C19" s="105"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="108"/>
       <c r="D19" s="58">
         <f>SUM(D16:D18)</f>
         <v>3</v>
@@ -2225,11 +2225,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="122"/>
-      <c r="C21" s="81"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="97"/>
       <c r="D21" s="19"/>
       <c r="E21" s="27">
         <f>SUM(E16:E18)</f>
@@ -2272,40 +2272,40 @@
       <c r="H23" s="35"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="83" t="s">
+      <c r="A24" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="83"/>
-      <c r="C24" s="83" t="s">
+      <c r="B24" s="99"/>
+      <c r="C24" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="83"/>
-      <c r="E24" s="123" t="s">
+      <c r="D24" s="99"/>
+      <c r="E24" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="123"/>
-      <c r="G24" s="83" t="s">
+      <c r="F24" s="102"/>
+      <c r="G24" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="83"/>
+      <c r="H24" s="99"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="84" t="s">
+      <c r="A25" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="84"/>
-      <c r="C25" s="84" t="s">
+      <c r="B25" s="100"/>
+      <c r="C25" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="84"/>
-      <c r="E25" s="124" t="s">
+      <c r="D25" s="100"/>
+      <c r="E25" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="124"/>
-      <c r="G25" s="84" t="s">
+      <c r="F25" s="103"/>
+      <c r="G25" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="84"/>
+      <c r="H25" s="100"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="34"/>
@@ -2348,25 +2348,36 @@
       <c r="H29" s="35"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="83" t="s">
+      <c r="A30" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="83"/>
-      <c r="C30" s="83" t="s">
+      <c r="B30" s="99"/>
+      <c r="C30" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="83"/>
-      <c r="E30" s="123" t="s">
+      <c r="D30" s="99"/>
+      <c r="E30" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="123"/>
-      <c r="G30" s="83" t="s">
+      <c r="F30" s="102"/>
+      <c r="G30" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="83"/>
+      <c r="H30" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A30:B30"/>
@@ -2380,17 +2391,6 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
@@ -2420,55 +2420,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="134"/>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="135" t="s">
+      <c r="A1" s="138"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="139" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="141" t="s">
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="142"/>
+      <c r="H1" s="146"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="134"/>
-      <c r="B2" s="134"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="141" t="s">
+      <c r="A2" s="138"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="142"/>
+      <c r="H2" s="146"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="134"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="141" t="s">
+      <c r="A3" s="138"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="142"/>
+      <c r="H3" s="146"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="133" t="str">
+      <c r="A4" s="137" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 31 tháng 07 năm 2026</v>
       </c>
-      <c r="B4" s="133"/>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
@@ -2505,27 +2505,27 @@
       <c r="H7" s="69"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="127" t="s">
+      <c r="A8" s="147" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="147" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="129" t="s">
+      <c r="C8" s="149" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="131"/>
-      <c r="G8" s="132" t="s">
+      <c r="D8" s="150"/>
+      <c r="E8" s="150"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="152" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="132"/>
+      <c r="H8" s="152"/>
       <c r="I8" s="33"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="128"/>
-      <c r="B9" s="128"/>
+      <c r="A9" s="148"/>
+      <c r="B9" s="148"/>
       <c r="C9" s="74" t="s">
         <v>60</v>
       </c>
@@ -2538,8 +2538,8 @@
       <c r="F9" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="132"/>
-      <c r="H9" s="132"/>
+      <c r="G9" s="152"/>
+      <c r="H9" s="152"/>
       <c r="I9" s="33"/>
     </row>
     <row r="10" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2666,10 +2666,10 @@
         <f>D14-E14</f>
         <v>2</v>
       </c>
-      <c r="G14" s="147" t="s">
+      <c r="G14" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="147"/>
+      <c r="H14" s="130"/>
       <c r="I14" s="33"/>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2692,10 +2692,10 @@
         <f t="shared" ref="F15" si="0">D15</f>
         <v>178</v>
       </c>
-      <c r="G15" s="147" t="s">
+      <c r="G15" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="147"/>
+      <c r="H15" s="130"/>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2718,10 +2718,10 @@
         <f>D16-E16</f>
         <v>52</v>
       </c>
-      <c r="G16" s="147" t="s">
+      <c r="G16" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="147"/>
+      <c r="H16" s="130"/>
     </row>
     <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55">
@@ -2743,10 +2743,10 @@
         <f>D17-E17</f>
         <v>22</v>
       </c>
-      <c r="G17" s="147" t="s">
+      <c r="G17" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="147"/>
+      <c r="H17" s="130"/>
     </row>
     <row r="18" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="55">
@@ -2768,10 +2768,10 @@
         <f>D18-E18</f>
         <v>2</v>
       </c>
-      <c r="G18" s="147" t="s">
+      <c r="G18" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="147"/>
+      <c r="H18" s="130"/>
     </row>
     <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="55">
@@ -2792,10 +2792,10 @@
       <c r="F19" s="23">
         <v>3</v>
       </c>
-      <c r="G19" s="147" t="s">
+      <c r="G19" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="147"/>
+      <c r="H19" s="130"/>
     </row>
     <row r="20" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="55">
@@ -2815,10 +2815,10 @@
         <f>SUM(D20-E20)</f>
         <v>23</v>
       </c>
-      <c r="G20" s="148" t="s">
+      <c r="G20" s="135" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="149"/>
+      <c r="H20" s="136"/>
     </row>
     <row r="21" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="55">
@@ -2840,16 +2840,16 @@
         <f>SUM(D21-E21)</f>
         <v>140</v>
       </c>
-      <c r="G21" s="147" t="s">
+      <c r="G21" s="130" t="s">
         <v>80</v>
       </c>
-      <c r="H21" s="147"/>
+      <c r="H21" s="130"/>
     </row>
     <row r="22" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="143" t="s">
+      <c r="A22" s="131" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="144"/>
+      <c r="B22" s="132"/>
       <c r="C22" s="56">
         <f>SUM(C10:C21)</f>
         <v>6660</v>
@@ -2866,8 +2866,8 @@
         <f>SUM(F10:F21)</f>
         <v>2936</v>
       </c>
-      <c r="G22" s="145"/>
-      <c r="H22" s="146"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="134"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="69"/>
@@ -2880,40 +2880,40 @@
       <c r="H23" s="69"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="152" t="s">
+      <c r="A24" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="152"/>
-      <c r="C24" s="152" t="s">
+      <c r="B24" s="129"/>
+      <c r="C24" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="152"/>
-      <c r="E24" s="152" t="s">
+      <c r="D24" s="129"/>
+      <c r="E24" s="129" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="152"/>
-      <c r="G24" s="83" t="s">
+      <c r="F24" s="129"/>
+      <c r="G24" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="83"/>
+      <c r="H24" s="99"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="151" t="s">
+      <c r="A25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="151"/>
-      <c r="C25" s="151" t="s">
+      <c r="B25" s="128"/>
+      <c r="C25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="151"/>
-      <c r="E25" s="151" t="s">
+      <c r="D25" s="128"/>
+      <c r="E25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="151"/>
-      <c r="G25" s="151" t="s">
+      <c r="F25" s="128"/>
+      <c r="G25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="151"/>
+      <c r="H25" s="128"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="75"/>
@@ -2956,22 +2956,22 @@
       <c r="H29" s="77"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="150" t="s">
+      <c r="A30" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="150"/>
-      <c r="C30" s="150" t="s">
+      <c r="B30" s="127"/>
+      <c r="C30" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="150"/>
-      <c r="E30" s="150" t="s">
+      <c r="D30" s="127"/>
+      <c r="E30" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="150"/>
-      <c r="G30" s="150" t="s">
+      <c r="F30" s="127"/>
+      <c r="G30" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="150"/>
+      <c r="H30" s="127"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="69"/>
@@ -2985,6 +2985,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H9"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G13:H13"/>
@@ -3001,26 +3021,6 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
